--- a/universe_analysis.xlsx
+++ b/universe_analysis.xlsx
@@ -18,9 +18,10 @@
     <sheet name="Insider F4 Leaders" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Insider Clusters Live" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Non-Biotech Top 100" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Unknown Mcap (cat)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Fund Coverage Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="All Funds (per-fund status)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Bill Miller Spotlight" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Unknown Mcap (cat)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Fund Coverage Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="All Funds (per-fund status)" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +97,7 @@
       <sz val="18"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +112,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FBF9F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4E4E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,6 +237,12 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -7229,6 +7241,1816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>BILL MILLER — BOTH FUNDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bill IV: Miller Value Partners LLC (Sarasota, FL — 55 holdings). Bill III: Patient Capital Management LLC (40 holdings). Top positions + shared overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>TOP 20 HOLDINGS BY FUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Value $M</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>%Book</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Mcap $M</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>13F #</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Activist %</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Cluster?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Bill IV — Miller Value Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>NABORS INDUSTRIES LTD</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>38247.6</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>444,430</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1389.23313552</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>CRGY</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>CRESCENT ENERGY COMPANY</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>27042.3</v>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>2,003,132</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>3447.82699632</v>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>GTN</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>GRAY MEDIA INC</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>23306.2</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>5,370,100</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>331.77302224</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>LNC-PD</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>LINCOLN NATL CORP IND</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>20259.5</v>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>570,690</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>5026.99494913</v>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>STATE STR SPDR S&amp;P 500 ETF T</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>19538.8</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>30,044</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F11" s="27" t="inlineStr"/>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>QUAD</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>QUAD / GRAPHICS INC</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>17523.4</v>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>2,651,039</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F12" s="28" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>BFH</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>BREAD FINANCIAL HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>14506</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>193,697</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>4138.08752665</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>TDAY</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>USA TODAY CO INC</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>13883.4</v>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>1,969,280</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1156.01263468</v>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>CNDT</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>CONDUENT INC</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>12830.6</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>10,023,930</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>217.1355396</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>UNITED PARCEL SVCS INC</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>11717.8</v>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>119,108</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>74862.09863762</v>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BLMN</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>BLOOMIN BRANDS INC</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>10998.4</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2,036,734</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>690.0511532200001</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>FOSL</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>FOSSIL GROUP INC</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>10452.5</v>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>2,425,185</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>253.54585542</v>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>CTO RLTY GROWTH INC NEW</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>10281.4</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>556,053</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>695.9419952000001</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>ITRN</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>ITURAN LOCATION AND CONTROL</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>9993.1</v>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>203,900</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>1297.26796458</v>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>VTRS</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>VIATRIS INC</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>9884.9</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>731,676</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>17899.17429198</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>CHRD</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>CHORD ENERGY CORPORATION</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>9857.299999999999</v>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>69,330</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>6931.55541096</v>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>JXN</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>JACKSON FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>8529.5</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>80,680</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>7449.260938240001</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>VERIZON COMMUNICATIONS INC</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>8433.6</v>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>168,000</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>189445.1077467</v>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>DCH</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>DAUCH CORP</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>8277.700000000001</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1,395,905</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1497.78407892</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>JELD</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>JELD-WEN HLDG INC</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>8208.700000000001</v>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>6,619,885</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>153.34935138</v>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Bill III — Patient Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>ROYALTY PHARMA PLC</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>174789.1</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>3,643,716</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>20555.491904</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>C-PR</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>CITIGROUP INC</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>160347</v>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>1,413,870</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>43890.41393581</v>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>ALPHABET INC</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>153555.2</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>533,993</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>4459051.48</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>AMAZON COM INC</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>136296</v>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>654,419</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>2628929.97506404</v>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>QXO</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>QXO INC</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>131636.3</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>6,778,389</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>12878.9842128</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>NVIDIA CORPORATION</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>124018.5</v>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>711,115</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>5098698</v>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>67</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>UNITEDHEALTH GROUP INC</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>118286.1</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>437,141</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>364129.58022784</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>ET-PI</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>ENERGY TRANSFER L P</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>117502.3</v>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>6,088,203</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>39435.68531442001</v>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>IAC INC</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>108063.6</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2,699,564</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F37" s="27" t="inlineStr"/>
+      <c r="G37" s="12" t="inlineStr"/>
+      <c r="H37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>NCLH</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>NORWEGIAN CRUISE LINE HLDGS</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>107518.3</v>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>5,749,640</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>9384.211261600001</v>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>SDRL</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>SEADRILL LTD</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>97947.2</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2,152,685</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>2409.92577832</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>META PLATFORMS INC</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>97883.60000000001</v>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>171,086</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F40" s="28" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>CVS HEALTH CORP</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>97471.2</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1,357,159</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>125449.17282424</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>COINBASE GLOBAL INC</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>75153.3</v>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>430,405</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>43004.47986</v>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>ADOBE INC</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>72262.8</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>297,279</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>77576.10000000001</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>CROX</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>CROCS INC</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>69972.8</v>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>842,842</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>6213.690482399999</v>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>BIOGEN INC</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>69618</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>379,741</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>29022.50445986</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>PGEN</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>PRECIGEN INC</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>68953.3</v>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>17,817,387</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>1718.3829236</v>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J46" s="20" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>UNITED AIRLS HLDGS INC</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>67397.10000000001</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>732,020</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>38403.09021695999</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>ILMN</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>ILLUMINA INC</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>67149.7</v>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>544,780</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>24500.009</v>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="20" t="inlineStr"/>
+    </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>SHARED OVERLAP — POSITIONS HELD BY BOTH FUNDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Bill IV %</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Bill III %</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Combined %</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Mcap $M</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>13F Universe</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Activist %</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>STATE STR SPDR S&amp;P 500 ETF T</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="F53" s="27" t="inlineStr"/>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State Street SPDR S&amp;P 500 ETF </t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>CROX</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>CROCS INC</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>6213.690482399999</v>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="20" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>OMF</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>ONEMAIN HLDGS INC</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>6721.59078736</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>OneMain Holdings, Inc.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A51:J51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7810,7 +9632,7 @@
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="29" t="inlineStr"/>
+      <c r="M13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -8196,7 +10018,7 @@
       <c r="J21" s="20" t="inlineStr"/>
       <c r="K21" s="20" t="inlineStr"/>
       <c r="L21" s="20" t="inlineStr"/>
-      <c r="M21" s="29" t="inlineStr"/>
+      <c r="M21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -8231,7 +10053,7 @@
       <c r="J22" s="12" t="inlineStr"/>
       <c r="K22" s="12" t="inlineStr"/>
       <c r="L22" s="12" t="inlineStr"/>
-      <c r="M22" s="30" t="inlineStr"/>
+      <c r="M22" s="32" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -9097,7 +10919,7 @@
       <c r="J40" s="12" t="inlineStr"/>
       <c r="K40" s="12" t="inlineStr"/>
       <c r="L40" s="12" t="inlineStr"/>
-      <c r="M40" s="30" t="inlineStr"/>
+      <c r="M40" s="32" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
@@ -9912,7 +11734,7 @@
       <c r="J57" s="20" t="inlineStr"/>
       <c r="K57" s="20" t="inlineStr"/>
       <c r="L57" s="20" t="inlineStr"/>
-      <c r="M57" s="29" t="inlineStr"/>
+      <c r="M57" s="31" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
@@ -9992,7 +11814,7 @@
       <c r="J59" s="20" t="inlineStr"/>
       <c r="K59" s="20" t="inlineStr"/>
       <c r="L59" s="20" t="inlineStr"/>
-      <c r="M59" s="29" t="inlineStr"/>
+      <c r="M59" s="31" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
@@ -10170,7 +11992,7 @@
       <c r="J63" s="20" t="inlineStr"/>
       <c r="K63" s="20" t="inlineStr"/>
       <c r="L63" s="20" t="inlineStr"/>
-      <c r="M63" s="29" t="inlineStr"/>
+      <c r="M63" s="31" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
@@ -10597,7 +12419,7 @@
       <c r="J72" s="12" t="inlineStr"/>
       <c r="K72" s="12" t="inlineStr"/>
       <c r="L72" s="12" t="inlineStr"/>
-      <c r="M72" s="30" t="inlineStr"/>
+      <c r="M72" s="32" t="inlineStr"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="17" t="inlineStr">
@@ -10877,7 +12699,7 @@
       <c r="J78" s="12" t="inlineStr"/>
       <c r="K78" s="12" t="inlineStr"/>
       <c r="L78" s="12" t="inlineStr"/>
-      <c r="M78" s="30" t="inlineStr"/>
+      <c r="M78" s="32" t="inlineStr"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="17" t="inlineStr">
@@ -10961,7 +12783,7 @@
       <c r="J80" s="12" t="inlineStr"/>
       <c r="K80" s="12" t="inlineStr"/>
       <c r="L80" s="12" t="inlineStr"/>
-      <c r="M80" s="30" t="inlineStr"/>
+      <c r="M80" s="32" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="17" t="inlineStr">
@@ -11045,7 +12867,7 @@
       <c r="J82" s="12" t="inlineStr"/>
       <c r="K82" s="12" t="inlineStr"/>
       <c r="L82" s="12" t="inlineStr"/>
-      <c r="M82" s="30" t="inlineStr"/>
+      <c r="M82" s="32" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="17" t="inlineStr">
@@ -11666,7 +13488,7 @@
       <c r="J95" s="20" t="inlineStr"/>
       <c r="K95" s="20" t="inlineStr"/>
       <c r="L95" s="20" t="inlineStr"/>
-      <c r="M95" s="29" t="inlineStr"/>
+      <c r="M95" s="31" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
@@ -11701,7 +13523,7 @@
       <c r="J96" s="12" t="inlineStr"/>
       <c r="K96" s="12" t="inlineStr"/>
       <c r="L96" s="12" t="inlineStr"/>
-      <c r="M96" s="30" t="inlineStr"/>
+      <c r="M96" s="32" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="17" t="inlineStr">
@@ -12222,7 +14044,7 @@
       <c r="J107" s="20" t="inlineStr"/>
       <c r="K107" s="20" t="inlineStr"/>
       <c r="L107" s="20" t="inlineStr"/>
-      <c r="M107" s="29" t="inlineStr"/>
+      <c r="M107" s="31" t="inlineStr"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
@@ -12919,7 +14741,7 @@
       <c r="J122" s="12" t="inlineStr"/>
       <c r="K122" s="12" t="inlineStr"/>
       <c r="L122" s="12" t="inlineStr"/>
-      <c r="M122" s="30" t="inlineStr"/>
+      <c r="M122" s="32" t="inlineStr"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="17" t="inlineStr">
@@ -13089,7 +14911,7 @@
       <c r="J126" s="12" t="inlineStr"/>
       <c r="K126" s="12" t="inlineStr"/>
       <c r="L126" s="12" t="inlineStr"/>
-      <c r="M126" s="30" t="inlineStr"/>
+      <c r="M126" s="32" t="inlineStr"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="17" t="inlineStr">
@@ -13218,7 +15040,7 @@
       <c r="J129" s="20" t="inlineStr"/>
       <c r="K129" s="20" t="inlineStr"/>
       <c r="L129" s="20" t="inlineStr"/>
-      <c r="M129" s="29" t="inlineStr"/>
+      <c r="M129" s="31" t="inlineStr"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="9" t="inlineStr">
@@ -13253,7 +15075,7 @@
       <c r="J130" s="12" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr"/>
       <c r="L130" s="12" t="inlineStr"/>
-      <c r="M130" s="30" t="inlineStr"/>
+      <c r="M130" s="32" t="inlineStr"/>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="17" t="inlineStr">
@@ -13729,7 +15551,7 @@
       <c r="J140" s="12" t="inlineStr"/>
       <c r="K140" s="12" t="inlineStr"/>
       <c r="L140" s="12" t="inlineStr"/>
-      <c r="M140" s="30" t="inlineStr"/>
+      <c r="M140" s="32" t="inlineStr"/>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="17" t="inlineStr">
@@ -13858,7 +15680,7 @@
       <c r="J143" s="20" t="inlineStr"/>
       <c r="K143" s="20" t="inlineStr"/>
       <c r="L143" s="20" t="inlineStr"/>
-      <c r="M143" s="29" t="inlineStr"/>
+      <c r="M143" s="31" t="inlineStr"/>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
@@ -15404,7 +17226,7 @@
       <c r="J175" s="20" t="inlineStr"/>
       <c r="K175" s="20" t="inlineStr"/>
       <c r="L175" s="20" t="inlineStr"/>
-      <c r="M175" s="29" t="inlineStr"/>
+      <c r="M175" s="31" t="inlineStr"/>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
@@ -15439,7 +17261,7 @@
       <c r="J176" s="12" t="inlineStr"/>
       <c r="K176" s="12" t="inlineStr"/>
       <c r="L176" s="12" t="inlineStr"/>
-      <c r="M176" s="30" t="inlineStr"/>
+      <c r="M176" s="32" t="inlineStr"/>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="17" t="inlineStr">
@@ -15474,7 +17296,7 @@
       <c r="J177" s="20" t="inlineStr"/>
       <c r="K177" s="20" t="inlineStr"/>
       <c r="L177" s="20" t="inlineStr"/>
-      <c r="M177" s="29" t="inlineStr"/>
+      <c r="M177" s="31" t="inlineStr"/>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
@@ -15558,7 +17380,7 @@
       <c r="J179" s="20" t="inlineStr"/>
       <c r="K179" s="20" t="inlineStr"/>
       <c r="L179" s="20" t="inlineStr"/>
-      <c r="M179" s="29" t="inlineStr"/>
+      <c r="M179" s="31" t="inlineStr"/>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
@@ -15732,7 +17554,7 @@
       <c r="J183" s="20" t="inlineStr"/>
       <c r="K183" s="20" t="inlineStr"/>
       <c r="L183" s="20" t="inlineStr"/>
-      <c r="M183" s="29" t="inlineStr"/>
+      <c r="M183" s="31" t="inlineStr"/>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
@@ -15861,7 +17683,7 @@
       <c r="J186" s="12" t="inlineStr"/>
       <c r="K186" s="12" t="inlineStr"/>
       <c r="L186" s="12" t="inlineStr"/>
-      <c r="M186" s="30" t="inlineStr"/>
+      <c r="M186" s="32" t="inlineStr"/>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="17" t="inlineStr">
@@ -16035,7 +17857,7 @@
       <c r="J190" s="12" t="inlineStr"/>
       <c r="K190" s="12" t="inlineStr"/>
       <c r="L190" s="12" t="inlineStr"/>
-      <c r="M190" s="30" t="inlineStr"/>
+      <c r="M190" s="32" t="inlineStr"/>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="17" t="inlineStr">
@@ -16070,7 +17892,7 @@
       <c r="J191" s="20" t="inlineStr"/>
       <c r="K191" s="20" t="inlineStr"/>
       <c r="L191" s="20" t="inlineStr"/>
-      <c r="M191" s="29" t="inlineStr"/>
+      <c r="M191" s="31" t="inlineStr"/>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
@@ -16244,7 +18066,7 @@
       <c r="J195" s="20" t="inlineStr"/>
       <c r="K195" s="20" t="inlineStr"/>
       <c r="L195" s="20" t="inlineStr"/>
-      <c r="M195" s="29" t="inlineStr"/>
+      <c r="M195" s="31" t="inlineStr"/>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="9" t="inlineStr">
@@ -16328,7 +18150,7 @@
       <c r="J197" s="20" t="inlineStr"/>
       <c r="K197" s="20" t="inlineStr"/>
       <c r="L197" s="20" t="inlineStr"/>
-      <c r="M197" s="29" t="inlineStr"/>
+      <c r="M197" s="31" t="inlineStr"/>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
@@ -16408,7 +18230,7 @@
       <c r="J199" s="20" t="inlineStr"/>
       <c r="K199" s="20" t="inlineStr"/>
       <c r="L199" s="20" t="inlineStr"/>
-      <c r="M199" s="29" t="inlineStr"/>
+      <c r="M199" s="31" t="inlineStr"/>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
@@ -16488,7 +18310,7 @@
       <c r="J201" s="20" t="inlineStr"/>
       <c r="K201" s="20" t="inlineStr"/>
       <c r="L201" s="20" t="inlineStr"/>
-      <c r="M201" s="29" t="inlineStr"/>
+      <c r="M201" s="31" t="inlineStr"/>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="9" t="inlineStr">
@@ -16523,7 +18345,7 @@
       <c r="J202" s="12" t="inlineStr"/>
       <c r="K202" s="12" t="inlineStr"/>
       <c r="L202" s="12" t="inlineStr"/>
-      <c r="M202" s="30" t="inlineStr"/>
+      <c r="M202" s="32" t="inlineStr"/>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="17" t="inlineStr">
@@ -16607,7 +18429,7 @@
       <c r="J204" s="12" t="inlineStr"/>
       <c r="K204" s="12" t="inlineStr"/>
       <c r="L204" s="12" t="inlineStr"/>
-      <c r="M204" s="30" t="inlineStr"/>
+      <c r="M204" s="32" t="inlineStr"/>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="17" t="inlineStr">
@@ -16642,7 +18464,7 @@
       <c r="J205" s="20" t="inlineStr"/>
       <c r="K205" s="20" t="inlineStr"/>
       <c r="L205" s="20" t="inlineStr"/>
-      <c r="M205" s="29" t="inlineStr"/>
+      <c r="M205" s="31" t="inlineStr"/>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="9" t="inlineStr">
@@ -16726,7 +18548,7 @@
       <c r="J207" s="20" t="inlineStr"/>
       <c r="K207" s="20" t="inlineStr"/>
       <c r="L207" s="20" t="inlineStr"/>
-      <c r="M207" s="29" t="inlineStr"/>
+      <c r="M207" s="31" t="inlineStr"/>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="9" t="inlineStr">
@@ -18403,7 +20225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18418,7 +20240,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>FUND COVERAGE</t>
         </is>
@@ -18614,7 +20436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -55443,13 +57265,13 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>135.2</v>
+        <v>114</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>16.13</v>
+        <v>16.16</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>1003.10270361</v>
@@ -57087,13 +58909,13 @@
         </is>
       </c>
       <c r="B42" s="25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="C42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>12.87</v>
+        <v>13.13</v>
       </c>
       <c r="E42" s="11" t="n">
         <v>417.4051581000001</v>

--- a/universe_analysis.xlsx
+++ b/universe_analysis.xlsx
@@ -24832,7 +24832,9 @@
       <c r="D12" s="13" t="n">
         <v>4.57</v>
       </c>
-      <c r="E12" s="18" t="inlineStr"/>
+      <c r="E12" s="11" t="n">
+        <v>363.474</v>
+      </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -25816,7 +25818,9 @@
       <c r="D40" s="13" t="n">
         <v>3.58</v>
       </c>
-      <c r="E40" s="18" t="inlineStr"/>
+      <c r="E40" s="11" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -35454,10 +35458,10 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>16358</v>
+        <v>72846</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>94.40000000000001</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -35506,10 +35510,10 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>67</v>
+        <v>607</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -35519,10 +35523,10 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -35769,7 +35773,7 @@
         <v>100407</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>20</v>
@@ -35827,7 +35831,7 @@
         <v>240291</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>15</v>
@@ -35885,7 +35889,7 @@
         <v>78051</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>66</v>
@@ -35972,7 +35976,7 @@
         <v>63930</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>32</v>
@@ -36134,7 +36138,7 @@
         <v>28981839</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>23</v>
@@ -36437,7 +36441,7 @@
         <v>75573</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>18</v>
@@ -36549,7 +36553,7 @@
         <v>6743695</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>1</v>
@@ -36578,7 +36582,7 @@
         <v>2000509</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>6</v>
@@ -36719,7 +36723,7 @@
         <v>14129284</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>14</v>
@@ -36827,7 +36831,7 @@
         <v>3085468</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>10</v>
@@ -36856,7 +36860,7 @@
         <v>9231521</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>35</v>
@@ -36914,7 +36918,7 @@
         <v>5623757</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>54</v>
@@ -36968,7 +36972,7 @@
         <v>9119078</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>15</v>
@@ -36997,7 +37001,7 @@
         <v>8670233</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>8</v>
@@ -37026,7 +37030,7 @@
         <v>7327697</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>11</v>
@@ -37138,7 +37142,7 @@
         <v>444980</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>13</v>
@@ -37196,7 +37200,7 @@
         <v>8934260</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>18</v>
@@ -37279,7 +37283,7 @@
         <v>30796448</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>46</v>
@@ -37337,7 +37341,7 @@
         <v>857578</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>2</v>
@@ -37366,7 +37370,7 @@
         <v>2716307</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>32</v>
@@ -37532,7 +37536,7 @@
         <v>21781443</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>24</v>
@@ -37590,7 +37594,7 @@
         <v>1716647</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>22</v>
@@ -37619,7 +37623,7 @@
         <v>2922</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>18</v>
@@ -37864,7 +37868,7 @@
         <v>10049753</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>37</v>
@@ -38072,7 +38076,7 @@
         <v>2032773</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>26</v>
@@ -38238,7 +38242,7 @@
         <v>35748671</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>10</v>
@@ -38321,7 +38325,7 @@
         <v>7499157</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>13</v>
@@ -38350,7 +38354,7 @@
         <v>3377</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>26</v>
@@ -38404,7 +38408,7 @@
         <v>5557999</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>24</v>
@@ -38462,7 +38466,7 @@
         <v>383179</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>1</v>
@@ -38607,7 +38611,7 @@
         <v>1884469</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G109" s="10" t="n">
         <v>36</v>
@@ -38748,7 +38752,7 @@
         <v>1432543</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" s="10" t="n">
         <v>0</v>
@@ -38777,7 +38781,7 @@
         <v>564065</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G115" s="10" t="n">
         <v>3</v>
@@ -38806,7 +38810,7 @@
         <v>1535497</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G116" s="10" t="n">
         <v>35</v>
@@ -38835,7 +38839,7 @@
         <v>7896331</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G117" s="10" t="n">
         <v>12</v>
@@ -38922,7 +38926,7 @@
         <v>11232639</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G120" s="10" t="n">
         <v>10</v>
@@ -38951,7 +38955,7 @@
         <v>3983380</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G121" s="10" t="n">
         <v>34</v>
@@ -39117,7 +39121,7 @@
         <v>1320592</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G127" s="10" t="n">
         <v>38</v>
@@ -39146,7 +39150,7 @@
         <v>2735138</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G128" s="10" t="n">
         <v>8</v>
@@ -39279,7 +39283,7 @@
         <v>4040158</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G133" s="10" t="n">
         <v>20</v>
@@ -39366,7 +39370,7 @@
         <v>5508093</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="10" t="n">
         <v>26</v>
@@ -39478,7 +39482,7 @@
         <v>7742273</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G140" s="10" t="n">
         <v>8</v>
@@ -39507,7 +39511,7 @@
         <v>12827767</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G141" s="10" t="n">
         <v>2</v>
@@ -39682,7 +39686,7 @@
         <v>7651890</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G148" s="10" t="n">
         <v>20</v>
@@ -39740,7 +39744,7 @@
         <v>2356319</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G150" s="10" t="n">
         <v>52</v>
@@ -39807,7 +39811,7 @@
         <v>1686714</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G153" s="10" t="n">
         <v>32</v>
@@ -39865,7 +39869,7 @@
         <v>321085</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" s="10" t="n">
         <v>13</v>
@@ -40002,7 +40006,7 @@
         <v>112449</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G160" s="10" t="n">
         <v>18</v>
@@ -40052,7 +40056,7 @@
         <v>4574765</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G162" s="10" t="n">
         <v>34</v>
@@ -40347,7 +40351,7 @@
         <v>91</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G173" s="10" t="n">
         <v>16</v>
@@ -40546,7 +40550,7 @@
         <v>772036</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G180" s="10" t="n">
         <v>8</v>
@@ -40633,7 +40637,7 @@
         <v>86390</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" s="10" t="n">
         <v>6</v>
@@ -40662,7 +40666,7 @@
         <v>4151193</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G184" s="10" t="n">
         <v>24</v>
@@ -40820,7 +40824,7 @@
         <v>3001999</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G190" s="10" t="n">
         <v>19</v>
@@ -40957,7 +40961,7 @@
         <v>256914</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G195" s="10" t="n">
         <v>8</v>
@@ -41015,7 +41019,7 @@
         <v>1301437</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G197" s="10" t="n">
         <v>44</v>
@@ -41189,7 +41193,7 @@
         <v>1219931</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G203" s="10" t="n">
         <v>13</v>
@@ -41704,7 +41708,7 @@
         <v>96402</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G222" s="10" t="n">
         <v>14</v>
@@ -42032,7 +42036,7 @@
         <v>3859778</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G234" s="10" t="n">
         <v>8</v>
@@ -42173,7 +42177,7 @@
         <v>26</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G239" s="10" t="n">
         <v>3</v>
@@ -42418,7 +42422,7 @@
         <v>1161567</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" s="10" t="n">
         <v>8</v>
@@ -42738,7 +42742,7 @@
         <v>1748117</v>
       </c>
       <c r="F260" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G260" s="10" t="n">
         <v>8</v>
@@ -43062,7 +43066,7 @@
         <v>12013</v>
       </c>
       <c r="F272" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G272" s="10" t="n">
         <v>22</v>
@@ -43091,7 +43095,7 @@
         <v>174444</v>
       </c>
       <c r="F273" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G273" s="10" t="n">
         <v>10</v>
@@ -43224,7 +43228,7 @@
         <v>39725</v>
       </c>
       <c r="F278" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" s="10" t="n">
         <v>3</v>
@@ -43523,7 +43527,7 @@
         <v>1325552</v>
       </c>
       <c r="F289" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G289" s="10" t="n">
         <v>9</v>
@@ -43610,7 +43614,7 @@
         <v>240901</v>
       </c>
       <c r="F292" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G292" s="10" t="n">
         <v>2</v>
@@ -43639,7 +43643,7 @@
         <v>132903</v>
       </c>
       <c r="F293" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G293" s="10" t="n">
         <v>4</v>
@@ -44267,7 +44271,7 @@
         <v>0</v>
       </c>
       <c r="F317" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G317" s="10" t="n">
         <v>18</v>
@@ -76388,7 +76392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -76544,7 +76548,9 @@
       <c r="D6" s="16" t="n">
         <v>18.57</v>
       </c>
-      <c r="E6" s="18" t="inlineStr"/>
+      <c r="E6" s="11" t="n">
+        <v>32850</v>
+      </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -76671,7 +76677,9 @@
       <c r="D9" s="16" t="n">
         <v>81.53</v>
       </c>
-      <c r="E9" s="18" t="inlineStr"/>
+      <c r="E9" s="11" t="n">
+        <v>97243.60665285001</v>
+      </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -76743,192 +76751,192 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>33.6</v>
+        <v>37.5</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>44.03</v>
+        <v>18.65</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3125.5596056</v>
+        <v>630.6543827099999</v>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G11" s="10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Calculating &amp; Accounting Machine</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>WGS</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>32.6</v>
+        <v>37.2</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>47.65</v>
+        <v>37.22</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1751.89047327</v>
+        <v>11984.0718474</v>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G12" s="10" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>GeneDx Holdings Corp.</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Services-Health Services</t>
+          <t>Hotels &amp; Motels</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>31.8</v>
+        <v>33.6</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>41.79</v>
+        <v>44.03</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>1203.028021</v>
+        <v>3125.5596056</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G13" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>Gold.com, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Wholesale-Jewelry, Watches, Prec</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>29.2</v>
+        <v>32.6</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>16.79</v>
+        <v>47.65</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>9384.211261600001</v>
+        <v>1751.89047327</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G14" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings Ltd.</t>
+          <t>GeneDx Holdings Corp.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Water Transportation</t>
+          <t>Services-Health Services</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>LRMR</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>25.6</v>
+        <v>31.8</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>5</v>
+        <v>41.79</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>378.13389068</v>
+        <v>1203.028021</v>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
@@ -76936,85 +76944,85 @@
         </is>
       </c>
       <c r="G15" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>Larimar Therapeutics, Inc.</t>
+          <t>Gold.com, Inc.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Wholesale-Jewelry, Watches, Prec</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>25</v>
+        <v>29.2</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4.44</v>
+        <v>16.79</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>344.06772624</v>
+        <v>9384.211261600001</v>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G16" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics Incorporated</t>
+          <t>Norwegian Cruise Line Holdings Ltd.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Water Transportation</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>VRDN</t>
+          <t>LRMR</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1714.1329262</v>
+        <v>378.13389068</v>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
@@ -77022,17 +77030,17 @@
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Viridian Therapeutics, Inc.</t>
+          <t>Larimar Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -77044,190 +77052,192 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>PRLD</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>186.17</v>
+        <v>4.44</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2361.99570048</v>
+        <v>344.06772624</v>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Alpha Metallurgical Resources, Inc.</t>
+          <t>Prelude Therapeutics Incorporated</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Bituminous Coal &amp; Lignite Surfac</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>VRDN</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>13.7</v>
+        <v>20</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>9.15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>206.29380608</v>
+        <v>1714.1329262</v>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>Lee Enterprises, Incorporated</t>
+          <t>Viridian Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Newspapers: Publishing or  Publi</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ZURA</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>6.25</v>
+        <v>186.17</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>356.2414125</v>
+        <v>2361.99570048</v>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G20" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>Zura Bio Limited</t>
+          <t>Alpha Metallurgical Resources, Inc.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Biological Products, (No Diagnos</t>
+          <t>Bituminous Coal &amp; Lignite Surfac</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>11.9</v>
+        <v>13.7</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="E21" s="18" t="inlineStr"/>
+        <v>9.15</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>206.29380608</v>
+      </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G21" s="10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>Oscar Health, Inc.</t>
+          <t>Lee Enterprises, Incorporated</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Hospital &amp; Medical Service Plans</t>
+          <t>Newspapers: Publishing or  Publi</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ZBIO</t>
+          <t>ZURA</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>19.96</v>
+        <v>6.25</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1248.77819706</v>
+        <v>356.2414125</v>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
@@ -77235,466 +77245,470 @@
         </is>
       </c>
       <c r="G22" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>Zenas BioPharma, Inc.</t>
+          <t>Zura Bio Limited</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Biological Products, (No Diagnos</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="E23" s="18" t="inlineStr"/>
+        <v>11.92</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>8468.4256</v>
+      </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>Sportradar Group AG</t>
+          <t>Oscar Health, Inc.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, D</t>
+          <t>Hospital &amp; Medical Service Plans</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>ZBIO</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>60.63</v>
+        <v>19.96</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>4.695e-05</v>
+        <v>1248.77819706</v>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G24" s="10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Zenas BioPharma, Inc.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Television Broadcasting Stations</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>NOMD</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>9.199999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>1427.1150831</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G25" s="10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Nomad Foods Limited</t>
+          <t>Sportradar Group AG</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Food and Kindred Products</t>
+          <t>Services-Computer Programming, D</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>142.49</v>
-      </c>
-      <c r="E26" s="18" t="inlineStr"/>
+        <v>60.63</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>4.695e-05</v>
+      </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="G26" s="10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>Reddit, Inc.</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; D</t>
+          <t>Television Broadcasting Stations</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>MLYS</t>
+          <t>NOMD</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>23.91</v>
+        <v>9.49</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>2031.92822763</v>
+        <v>1427.1150831</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G27" s="10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Mineralys Therapeutics, Inc.</t>
+          <t>Nomad Foods Limited</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Food and Kindred Products</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>34.05</v>
+        <v>142.49</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1382.48777204</v>
+        <v>33508.15951608</v>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G28" s="10" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>Insperity, Inc.</t>
+          <t>Reddit, Inc.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Services-Help Supply Services</t>
+          <t>Services-Computer Processing &amp; D</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>KOS</t>
+          <t>MLYS</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>1.9</v>
+        <v>23.91</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1453.3137213</v>
+        <v>2031.92822763</v>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G29" s="10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Kosmos Energy Ltd.</t>
+          <t>Mineralys Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Crude Petroleum &amp; Natural Gas</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="E30" s="18" t="inlineStr"/>
+        <v>34.05</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1382.48777204</v>
+      </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G30" s="10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Millrose Properties, Inc.</t>
+          <t>Insperity, Inc.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Services-Help Supply Services</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>KOS</t>
         </is>
       </c>
       <c r="B31" s="17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>28.88</v>
+        <v>1.9</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3103.92618267</v>
+        <v>1453.3137213</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G31" s="10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Upstart Holdings, Inc.</t>
+          <t>Kosmos Energy Ltd.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Finance Services</t>
+          <t>Crude Petroleum &amp; Natural Gas</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="B32" s="17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>2.66</v>
+        <v>27.52</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>155.224251</v>
+        <v>4714.4993148</v>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G32" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Millrose Properties, Inc.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Services-Advertising</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B33" s="17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>20.88</v>
+        <v>28.88</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>2548.96631348</v>
+        <v>3103.92618267</v>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
@@ -77702,42 +77716,42 @@
         </is>
       </c>
       <c r="G33" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H33" s="10" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>Six Flags Entertainment Corporation</t>
+          <t>Upstart Holdings, Inc.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Services-Amusement &amp; Recreation </t>
+          <t>Finance Services</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="C34" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>4.83</v>
+        <v>2.66</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>107.66172513</v>
+        <v>155.224251</v>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
@@ -77745,42 +77759,42 @@
         </is>
       </c>
       <c r="G34" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Empery Digital Inc.</t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Finance Services</t>
+          <t>Services-Advertising</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>PAGS</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="C35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>9.960000000000001</v>
+        <v>20.88</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>2313.38551374</v>
+        <v>2548.96631348</v>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
@@ -77788,85 +77802,85 @@
         </is>
       </c>
       <c r="G35" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>PagSeguro Digital Ltd.</t>
+          <t>Six Flags Entertainment Corporation</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; D</t>
+          <t xml:space="preserve">Services-Amusement &amp; Recreation </t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>EMPD</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="C36" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>87.73</v>
+        <v>4.83</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>8668.250406840001</v>
+        <v>107.66172513</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G36" s="10" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Builders FirstSource, Inc.</t>
+          <t>Empery Digital Inc.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Retail-Lumber &amp; Other Building M</t>
+          <t>Finance Services</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>PAGS</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>63.08</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4302.405303680001</v>
+        <v>2313.38551374</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -77874,42 +77888,42 @@
         </is>
       </c>
       <c r="G37" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>PagSeguro Digital Ltd.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Services-Computer Processing &amp; D</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>PATK</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="C38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>99.09999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2873.88089351</v>
+        <v>8668.250406840001</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -77917,85 +77931,85 @@
         </is>
       </c>
       <c r="G38" s="10" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>Patrick Industries, Inc.</t>
+          <t>Builders FirstSource, Inc.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Motor Vehicle Parts &amp; Accessorie</t>
+          <t>Retail-Lumber &amp; Other Building M</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>ANNX</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>5.62</v>
+        <v>63.08</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>188.9614685</v>
+        <v>4302.405303680001</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G39" s="10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>Annexon, Inc.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>PATK</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="C40" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>8.609999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>6540.79675116</v>
+        <v>2873.88089351</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -78003,83 +78017,85 @@
         </is>
       </c>
       <c r="G40" s="10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>Avantor, Inc.</t>
+          <t>Patrick Industries, Inc.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Laboratory Analytical Instrument</t>
+          <t>Motor Vehicle Parts &amp; Accessorie</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ANNX</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="C41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E41" s="18" t="inlineStr"/>
+        <v>5.62</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>188.9614685</v>
+      </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G41" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>DraftKings Inc.</t>
+          <t>Annexon, Inc.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Services-Miscellaneous Amusement</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="C42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>14.16</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>4179.8020369</v>
+        <v>6540.79675116</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -78087,85 +78103,85 @@
         </is>
       </c>
       <c r="G42" s="10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>GPGI, Inc.</t>
+          <t>Avantor, Inc.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Finance Services</t>
+          <t>Laboratory Analytical Instrument</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="C43" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>4.73</v>
+        <v>21.85</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>263.24508972</v>
+        <v>13045.92289</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G43" s="10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>Portillo's Inc.</t>
+          <t>DraftKings Inc.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Retail-Eating  Places</t>
+          <t>Services-Miscellaneous Amusement</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>LPX</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="C44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>85.48999999999999</v>
+        <v>14.16</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>5418.7200928</v>
+        <v>4179.8020369</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -78173,50 +78189,50 @@
         </is>
       </c>
       <c r="G44" s="10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Louisiana-Pacific Corporation</t>
+          <t>GPGI, Inc.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Lumber &amp; Wood Products (No Furni</t>
+          <t>Finance Services</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>XRAY</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="C45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>11.66</v>
+        <v>4.73</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>2069.37463539</v>
+        <v>263.24508972</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G45" s="10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H45" s="10" t="n">
         <v>0</v>
@@ -78226,116 +78242,118 @@
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>DENTSPLY SIRONA Inc.</t>
+          <t>Portillo's Inc.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Dental Equipment &amp; Supplies</t>
+          <t>Retail-Eating  Places</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>CLBR</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="C46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" s="18" t="inlineStr"/>
+        <v>49.52</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>25521.53576996</v>
+      </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G46" s="10" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Colombier Acquisition Corp. III</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Blank Checks</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>LOGC</t>
+          <t>LPX</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>9.16</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>426.2086328</v>
+        <v>5418.7200928</v>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>ContextLogic Holdings Inc.</t>
+          <t>Louisiana-Pacific Corporation</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Retail-Catalog &amp; Mail-Order Hous</t>
+          <t>Lumber &amp; Wood Products (No Furni</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>RLI</t>
+          <t>XRAY</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>53.56</v>
+        <v>11.66</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4881.00599279</v>
+        <v>2069.37463539</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -78343,39 +78361,39 @@
         </is>
       </c>
       <c r="G48" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>RLI Corp.</t>
+          <t>DENTSPLY SIRONA Inc.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Fire, Marine &amp; Casualty Insuranc</t>
+          <t>Dental Equipment &amp; Supplies</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>CLBR</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="12" t="inlineStr">
@@ -78384,34 +78402,42 @@
         </is>
       </c>
       <c r="G49" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="12" t="inlineStr"/>
-      <c r="K49" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>Colombier Acquisition Corp. III</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Blank Checks</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>GOGO</t>
+          <t>LOGC</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>4.55</v>
+        <v>9.16</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>461.1633634299999</v>
+        <v>426.2086328</v>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
@@ -78419,7 +78445,7 @@
         </is>
       </c>
       <c r="G50" s="10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>1</v>
@@ -78429,32 +78455,32 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Gogo Inc.</t>
+          <t>ContextLogic Holdings Inc.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Communications Services, NEC</t>
+          <t>Retail-Catalog &amp; Mail-Order Hous</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>RLI</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="C51" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>9.869999999999999</v>
+        <v>53.56</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>3168.95391477</v>
+        <v>4881.00599279</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -78462,50 +78488,48 @@
         </is>
       </c>
       <c r="G51" s="10" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>Graphic Packaging Holding Company</t>
+          <t>RLI Corp.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Paperboard Containers &amp; Boxes</t>
+          <t>Fire, Marine &amp; Casualty Insuranc</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>417.4051581000001</v>
-      </c>
+        <v>13.6</v>
+      </c>
+      <c r="E52" s="18" t="inlineStr"/>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G52" s="10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>0</v>
@@ -78513,77 +78537,69 @@
       <c r="I52" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="12" t="inlineStr">
-        <is>
-          <t>Benitec Biopharma Inc.</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Pharmaceutical Preparations</t>
-        </is>
-      </c>
+      <c r="J52" s="12" t="inlineStr"/>
+      <c r="K52" s="12" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>VAC</t>
+          <t>GOGO</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>67.47</v>
+        <v>4.55</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3364.58998008</v>
+        <v>461.1633634299999</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G53" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>Marriott Vacations Worldwide Corporati</t>
+          <t>Gogo Inc.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Real Estate Agents &amp; Managers (F</t>
+          <t>Communications Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>CPRI</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C54" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>17.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>2340.54773952</v>
+        <v>3168.95391477</v>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
@@ -78591,29 +78607,29 @@
         </is>
       </c>
       <c r="G54" s="10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Capri Holdings Limited</t>
+          <t>Graphic Packaging Holding Company</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Leather &amp; Leather Products</t>
+          <t>Paperboard Containers &amp; Boxes</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>ABCL</t>
+          <t>BNTC</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
@@ -78623,10 +78639,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>3.72</v>
+        <v>13.44</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1688.72592329</v>
+        <v>417.4051581000001</v>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
@@ -78634,17 +78650,17 @@
         </is>
       </c>
       <c r="G55" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>AbCellera Biologics Inc.</t>
+          <t>Benitec Biopharma Inc.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -78656,7 +78672,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>IMNM</t>
+          <t>VAC</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
@@ -78666,10 +78682,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>20.43</v>
+        <v>67.47</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>2122.31238356</v>
+        <v>3364.58998008</v>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
@@ -78677,42 +78693,42 @@
         </is>
       </c>
       <c r="G56" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>Immunome, Inc.</t>
+          <t>Marriott Vacations Worldwide Corporati</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Real Estate Agents &amp; Managers (F</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>CPRI</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>31.32</v>
+        <v>17.98</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>4161.24638874</v>
+        <v>2340.54773952</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -78723,39 +78739,39 @@
         <v>22</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>KBR, Inc.</t>
+          <t>Capri Holdings Limited</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Heavy Construction Other Than Bl</t>
+          <t>Leather &amp; Leather Products</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>35.84</v>
+        <v>3.72</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1213.1724871</v>
+        <v>1688.72592329</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -78763,50 +78779,50 @@
         </is>
       </c>
       <c r="G58" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>Gibraltar Industries, Inc.</t>
+          <t>AbCellera Biologics Inc.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Steel Works, Blast Furnaces &amp; Ro</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>IMNM</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C59" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>4.58</v>
+        <v>20.43</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>428.7948734</v>
+        <v>2122.31238356</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G59" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H59" s="10" t="n">
         <v>0</v>
@@ -78816,32 +78832,32 @@
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>Myriad Genetics, Inc.</t>
+          <t>Immunome, Inc.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>In Vitro &amp; In Vivo Diagnostic Su</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>29.38</v>
+        <v>31.32</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>7873.723088</v>
+        <v>4161.24638874</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -78849,42 +78865,42 @@
         </is>
       </c>
       <c r="G60" s="10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>Celsius Holdings, Inc.</t>
+          <t>KBR, Inc.</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>Bottled &amp; Canned Soft Drinks &amp; C</t>
+          <t>Heavy Construction Other Than Bl</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>MBC</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>8.73</v>
+        <v>35.84</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>1159.5403854</v>
+        <v>1213.1724871</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -78892,29 +78908,29 @@
         </is>
       </c>
       <c r="G61" s="10" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>MasterBrand, Inc.</t>
+          <t>Gibraltar Industries, Inc.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>Wood Household Furniture, (No Up</t>
+          <t>Steel Works, Blast Furnaces &amp; Ro</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>EOSE</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
@@ -78924,40 +78940,40 @@
         <v>1</v>
       </c>
       <c r="D62" s="16" t="n">
-        <v>6.13</v>
+        <v>4.58</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2597.28230655</v>
+        <v>428.7948734</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G62" s="10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>Eos Energy Enterprises, Inc.</t>
+          <t>Myriad Genetics, Inc.</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>Miscellaneous Electrical Machine</t>
+          <t>In Vitro &amp; In Vivo Diagnostic Su</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
@@ -78967,10 +78983,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="16" t="n">
-        <v>69.19</v>
+        <v>29.38</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>9104.227219440001</v>
+        <v>7873.723088</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -78978,7 +78994,7 @@
         </is>
       </c>
       <c r="G63" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63" s="10" t="n">
         <v>2</v>
@@ -78988,32 +79004,32 @@
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>Henry Schein, Inc.</t>
+          <t>Celsius Holdings, Inc.</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
         <is>
-          <t>Wholesale-Medical, Dental &amp; Hosp</t>
+          <t>Bottled &amp; Canned Soft Drinks &amp; C</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>MBC</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D64" s="16" t="n">
-        <v>3.46</v>
+        <v>8.73</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1155.25646496</v>
+        <v>1159.5403854</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -79021,85 +79037,85 @@
         </is>
       </c>
       <c r="G64" s="10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>Absci Corporation</t>
+          <t>MasterBrand, Inc.</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>Services-Commercial Physical &amp; B</t>
+          <t>Wood Household Furniture, (No Up</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>EOSE</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C65" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="16" t="n">
-        <v>12.19</v>
+        <v>6.13</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>191.976192</v>
+        <v>2597.28230655</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G65" s="10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>WW International, Inc.</t>
+          <t>Eos Energy Enterprises, Inc.</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>Services-Personal Services</t>
+          <t>Miscellaneous Electrical Machine</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>VFC</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C66" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="16" t="n">
-        <v>17.17</v>
+        <v>69.19</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>6789.368987649999</v>
+        <v>9104.227219440001</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -79107,50 +79123,50 @@
         </is>
       </c>
       <c r="G66" s="10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>V.F. Corporation</t>
+          <t>Henry Schein, Inc.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>Men's &amp; Boys' Furnishgs, Work Cl</t>
+          <t>Wholesale-Medical, Dental &amp; Hosp</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>RAL</t>
+          <t>ABSI</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C67" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="16" t="n">
-        <v>40.44</v>
+        <v>3.46</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>7631.602030640001</v>
+        <v>1155.25646496</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G67" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H67" s="10" t="n">
         <v>1</v>
@@ -79160,62 +79176,62 @@
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>Ralliant Corporation</t>
+          <t>Absci Corporation</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>Industrial Instruments For Measu</t>
+          <t>Services-Commercial Physical &amp; B</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="16" t="n">
-        <v>52.84</v>
+        <v>12.19</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>2703.34493291</v>
+        <v>191.976192</v>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G68" s="10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>Freshpet, Inc.</t>
+          <t>WW International, Inc.</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>Grain Mill Products</t>
+          <t>Services-Personal Services</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>TREX</t>
+          <t>VFC</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
@@ -79225,10 +79241,10 @@
         <v>1</v>
       </c>
       <c r="D69" s="16" t="n">
-        <v>40.38</v>
+        <v>17.17</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>4896.74709777</v>
+        <v>6789.368987649999</v>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
@@ -79236,7 +79252,7 @@
         </is>
       </c>
       <c r="G69" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H69" s="10" t="n">
         <v>1</v>
@@ -79246,19 +79262,19 @@
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>Trex Company, Inc.</t>
+          <t>V.F. Corporation</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>Lumber &amp; Wood Products (No Furni</t>
+          <t>Men's &amp; Boys' Furnishgs, Work Cl</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>RAL</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
@@ -79268,40 +79284,40 @@
         <v>1</v>
       </c>
       <c r="D70" s="16" t="n">
-        <v>11.05</v>
+        <v>40.44</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>1405.9267788</v>
+        <v>7631.602030640001</v>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G70" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Ralliant Corporation</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; D</t>
+          <t>Industrial Instruments For Measu</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
@@ -79311,40 +79327,40 @@
         <v>1</v>
       </c>
       <c r="D71" s="16" t="n">
-        <v>11</v>
+        <v>52.84</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1926.03126165</v>
+        <v>2703.34493291</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G71" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>ADMA Biologics, Inc.</t>
+          <t>Freshpet, Inc.</t>
         </is>
       </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>Biological Products, (No Diagnos</t>
+          <t>Grain Mill Products</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>OCUL</t>
+          <t>TREX</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
@@ -79354,10 +79370,10 @@
         <v>1</v>
       </c>
       <c r="D72" s="16" t="n">
-        <v>7.66</v>
+        <v>40.38</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>2064.79617594</v>
+        <v>4896.74709777</v>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
@@ -79365,29 +79381,29 @@
         </is>
       </c>
       <c r="G72" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>Ocular Therapeutix, Inc.</t>
+          <t>Trex Company, Inc.</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Lumber &amp; Wood Products (No Furni</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B73" s="17" t="n">
@@ -79397,96 +79413,96 @@
         <v>1</v>
       </c>
       <c r="D73" s="16" t="n">
-        <v>23.84</v>
+        <v>11.05</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3642.0123751</v>
+        <v>1405.9267788</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G73" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life, Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Services-Computer Processing &amp; D</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>HRI</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="B74" s="17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C74" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="16" t="n">
-        <v>142.47</v>
+        <v>11</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>5179.93007112</v>
+        <v>1926.03126165</v>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G74" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>Herc Holdings Inc.</t>
+          <t>ADMA Biologics, Inc.</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>Services-Miscellaneous Equipment</t>
+          <t>Biological Products, (No Diagnos</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>OCUL</t>
         </is>
       </c>
       <c r="B75" s="17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C75" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="16" t="n">
-        <v>18.66</v>
+        <v>7.66</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2702.23731234</v>
+        <v>2064.79617594</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -79494,85 +79510,85 @@
         </is>
       </c>
       <c r="G75" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Ocular Therapeutix, Inc.</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
         <is>
-          <t>Motorcycles, Bicycles &amp; Parts</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="B76" s="17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C76" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="16" t="n">
-        <v>3.53</v>
+        <v>23.84</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>56.10848334000001</v>
+        <v>3642.0123751</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G76" s="10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>TransAct Technologies Incorporated</t>
+          <t>F&amp;G Annuities &amp; Life, Inc.</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>Computer Peripheral Equipment, N</t>
+          <t>Life Insurance</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>HRI</t>
         </is>
       </c>
       <c r="B77" s="17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C77" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="16" t="n">
-        <v>77.38</v>
+        <v>142.47</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>2928.59983362</v>
+        <v>5179.93007112</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -79580,42 +79596,42 @@
         </is>
       </c>
       <c r="G77" s="10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>Maximus, Inc.</t>
+          <t>Herc Holdings Inc.</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Services-Miscellaneous Equipment</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>LQDA</t>
+          <t>HOG</t>
         </is>
       </c>
       <c r="B78" s="17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C78" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="16" t="n">
-        <v>59.98</v>
+        <v>18.66</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>6320.119995929999</v>
+        <v>2702.23731234</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -79623,50 +79639,50 @@
         </is>
       </c>
       <c r="G78" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>Liquidia Corporation</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Motorcycles, Bicycles &amp; Parts</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>TACT</t>
         </is>
       </c>
       <c r="B79" s="17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C79" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D79" s="16" t="n">
-        <v>31.77</v>
+        <v>3.53</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2194.7835</v>
+        <v>56.10848334000001</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G79" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H79" s="10" t="n">
         <v>0</v>
@@ -79676,19 +79692,19 @@
       </c>
       <c r="J79" s="12" t="inlineStr">
         <is>
-          <t>Phibro Animal Health Corporation</t>
+          <t>TransAct Technologies Incorporated</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Computer Peripheral Equipment, N</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>KVYO</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="B80" s="17" t="n">
@@ -79698,38 +79714,40 @@
         <v>1</v>
       </c>
       <c r="D80" s="16" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="E80" s="18" t="inlineStr"/>
+        <v>77.38</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>2928.59983362</v>
+      </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G80" s="10" t="n">
         <v>15</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>Klaviyo, Inc.</t>
+          <t>Maximus, Inc.</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>LQDA</t>
         </is>
       </c>
       <c r="B81" s="17" t="n">
@@ -79739,40 +79757,40 @@
         <v>1</v>
       </c>
       <c r="D81" s="16" t="n">
-        <v>8.98</v>
+        <v>59.98</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1414.95496649</v>
+        <v>6320.119995929999</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G81" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="12" t="inlineStr">
         <is>
-          <t>O-I Glass, Inc.</t>
+          <t>Liquidia Corporation</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
         <is>
-          <t>Glass Containers</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="B82" s="17" t="n">
@@ -79782,40 +79800,40 @@
         <v>1</v>
       </c>
       <c r="D82" s="16" t="n">
-        <v>10.99</v>
+        <v>31.77</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1924.9988572</v>
+        <v>2194.7835</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G82" s="10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H82" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>Flywire Corporation</t>
+          <t>Phibro Animal Health Corporation</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>KVYO</t>
         </is>
       </c>
       <c r="B83" s="17" t="n">
@@ -79825,26 +79843,28 @@
         <v>1</v>
       </c>
       <c r="D83" s="16" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="E83" s="18" t="inlineStr"/>
+        <v>18.38</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>4032.55300475</v>
+      </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
       <c r="G83" s="10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="12" t="inlineStr">
         <is>
-          <t>Okta, Inc.</t>
+          <t>Klaviyo, Inc.</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -79856,7 +79876,7 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>WBI</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="B84" s="17" t="n">
@@ -79866,38 +79886,40 @@
         <v>1</v>
       </c>
       <c r="D84" s="16" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E84" s="18" t="inlineStr"/>
+        <v>8.98</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>1414.95496649</v>
+      </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G84" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>WaterBridge Infrastructure LLC</t>
+          <t>O-I Glass, Inc.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Field Services, NEC</t>
+          <t>Glass Containers</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>CODI</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B85" s="17" t="n">
@@ -79907,10 +79929,10 @@
         <v>1</v>
       </c>
       <c r="D85" s="16" t="n">
-        <v>8.58</v>
+        <v>10.99</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>760.63561626</v>
+        <v>1924.9988572</v>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
@@ -79918,29 +79940,29 @@
         </is>
       </c>
       <c r="G85" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" s="12" t="inlineStr">
         <is>
-          <t>Compass Diversified</t>
+          <t>Flywire Corporation</t>
         </is>
       </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
-          <t>Household Furniture</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B86" s="17" t="n">
@@ -79950,16 +79972,18 @@
         <v>1</v>
       </c>
       <c r="D86" s="16" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="E86" s="18" t="inlineStr"/>
+        <v>72.16</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>20749.75749</v>
+      </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
       <c r="G86" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H86" s="10" t="n">
         <v>0</v>
@@ -79969,7 +79993,7 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>GitLab Inc.</t>
+          <t>Okta, Inc.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -79981,136 +80005,136 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>DBD</t>
+          <t>WBI</t>
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C87" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D87" s="16" t="n">
-        <v>76.68000000000001</v>
+        <v>19.97</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2902.20553352</v>
+        <v>1456.70767283</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G87" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" s="12" t="inlineStr">
         <is>
-          <t>Diebold Nixdorf, Incorporated</t>
+          <t>WaterBridge Infrastructure LLC</t>
         </is>
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>Calculating &amp; Accounting Machine</t>
+          <t>Oil &amp; Gas Field Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>CODI</t>
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C88" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D88" s="16" t="n">
-        <v>9.15</v>
+        <v>8.58</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>3422.4887892</v>
+        <v>760.63561626</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G88" s="10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I88" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>NovaGold Resources Inc.</t>
+          <t>Compass Diversified</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>Gold and Silver Ores</t>
+          <t>Household Furniture</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>NFBK</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C89" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D89" s="16" t="n">
-        <v>13.13</v>
+        <v>27.01</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>601.81710732</v>
+        <v>4513.81888</v>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G89" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>Northfield Bancorp, Inc.</t>
+          <t>GitLab Inc.</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
-          <t>Savings Institution, Federally C</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="B90" s="17" t="n">
@@ -80120,18 +80144,18 @@
         <v>1</v>
       </c>
       <c r="D90" s="16" t="n">
-        <v>13.47</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>191.86709808</v>
+        <v>2902.20553352</v>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G90" s="10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H90" s="10" t="n">
         <v>0</v>
@@ -80141,19 +80165,19 @@
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>Anika Therapeutics, Inc.</t>
+          <t>Diebold Nixdorf, Incorporated</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>Surgical &amp; Medical Instruments &amp;</t>
+          <t>Calculating &amp; Accounting Machine</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>COTY</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="B91" s="17" t="n">
@@ -80163,18 +80187,18 @@
         <v>1</v>
       </c>
       <c r="D91" s="16" t="n">
-        <v>2.53</v>
+        <v>9.15</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>1716.9095541</v>
+        <v>3422.4887892</v>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G91" s="10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H91" s="10" t="n">
         <v>0</v>
@@ -80184,19 +80208,19 @@
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>Coty Inc.</t>
+          <t>NovaGold Resources Inc.</t>
         </is>
       </c>
       <c r="K91" s="12" t="inlineStr">
         <is>
-          <t>Perfumes, Cosmetics &amp; Other Toil</t>
+          <t>Gold and Silver Ores</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>ARKO</t>
+          <t>NFBK</t>
         </is>
       </c>
       <c r="B92" s="17" t="n">
@@ -80206,10 +80230,10 @@
         <v>1</v>
       </c>
       <c r="D92" s="16" t="n">
-        <v>5.05</v>
+        <v>13.13</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>840.2710502900001</v>
+        <v>601.81710732</v>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
@@ -80217,29 +80241,29 @@
         </is>
       </c>
       <c r="G92" s="10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>Arko Corp.</t>
+          <t>Northfield Bancorp, Inc.</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>Retail-Convenience Stores</t>
+          <t>Savings Institution, Federally C</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>EEFT</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="B93" s="17" t="n">
@@ -80249,40 +80273,40 @@
         <v>1</v>
       </c>
       <c r="D93" s="16" t="n">
-        <v>66.87</v>
+        <v>13.47</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>2506.86418896</v>
+        <v>191.86709808</v>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G93" s="10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>Euronet Worldwide, Inc.</t>
+          <t>Anika Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Functions Related To Depository </t>
+          <t>Surgical &amp; Medical Instruments &amp;</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>AVD</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="B94" s="17" t="n">
@@ -80292,14 +80316,14 @@
         <v>1</v>
       </c>
       <c r="D94" s="16" t="n">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>75.80562175</v>
+        <v>1716.9095541</v>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G94" s="10" t="n">
@@ -80309,23 +80333,23 @@
         <v>0</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>American Vanguard Corporation</t>
+          <t>Coty Inc.</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>Agricultural Chemicals</t>
+          <t>Perfumes, Cosmetics &amp; Other Toil</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>TNET</t>
+          <t>ARKO</t>
         </is>
       </c>
       <c r="B95" s="17" t="n">
@@ -80335,40 +80359,40 @@
         <v>1</v>
       </c>
       <c r="D95" s="16" t="n">
-        <v>37.7</v>
+        <v>5.05</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>2080.83288147</v>
+        <v>840.2710502900001</v>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G95" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H95" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>TriNet Group, Inc.</t>
+          <t>Arko Corp.</t>
         </is>
       </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Retail-Convenience Stores</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>EEFT</t>
         </is>
       </c>
       <c r="B96" s="17" t="n">
@@ -80378,10 +80402,10 @@
         <v>1</v>
       </c>
       <c r="D96" s="16" t="n">
-        <v>186.59</v>
+        <v>66.87</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>5844.145806240001</v>
+        <v>2506.86418896</v>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
@@ -80389,29 +80413,29 @@
         </is>
       </c>
       <c r="G96" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H96" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>Morningstar, Inc.</t>
+          <t>Euronet Worldwide, Inc.</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>Investment Advice</t>
+          <t xml:space="preserve">Functions Related To Depository </t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>SPB</t>
+          <t>AVD</t>
         </is>
       </c>
       <c r="B97" s="17" t="n">
@@ -80421,40 +80445,40 @@
         <v>1</v>
       </c>
       <c r="D97" s="16" t="n">
-        <v>72.84999999999999</v>
+        <v>2.77</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>1947.62520306</v>
+        <v>75.80562175</v>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G97" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I97" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>Spectrum Brands Holdings, Inc.</t>
+          <t>American Vanguard Corporation</t>
         </is>
       </c>
       <c r="K97" s="12" t="inlineStr">
         <is>
-          <t>Miscellaneous Electrical Machine</t>
+          <t>Agricultural Chemicals</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>TNET</t>
         </is>
       </c>
       <c r="B98" s="17" t="n">
@@ -80464,10 +80488,10 @@
         <v>1</v>
       </c>
       <c r="D98" s="16" t="n">
-        <v>18.41</v>
+        <v>37.7</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>6857.66202862</v>
+        <v>2080.83288147</v>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
@@ -80475,7 +80499,7 @@
         </is>
       </c>
       <c r="G98" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
@@ -80485,19 +80509,19 @@
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>Healthcare Realty Trust Incorporated</t>
+          <t>TriNet Group, Inc.</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B99" s="17" t="n">
@@ -80507,51 +80531,53 @@
         <v>1</v>
       </c>
       <c r="D99" s="16" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="E99" s="18" t="inlineStr"/>
+        <v>186.59</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>5844.145806240001</v>
+      </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G99" s="10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>Medline Inc.</t>
+          <t>Morningstar, Inc.</t>
         </is>
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>Surgical &amp; Medical Instruments &amp;</t>
+          <t>Investment Advice</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>SPB</t>
         </is>
       </c>
       <c r="B100" s="17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C100" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D100" s="16" t="n">
-        <v>30.66</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>1530.00103608</v>
+        <v>1947.62520306</v>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
@@ -80559,115 +80585,115 @@
         </is>
       </c>
       <c r="G100" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H100" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>Concentrix Corporation</t>
+          <t>Spectrum Brands Holdings, Inc.</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Miscellaneous Electrical Machine</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B101" s="17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C101" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101" s="16" t="n">
-        <v>21.37</v>
+        <v>18.41</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>142.81204352</v>
+        <v>6857.66202862</v>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G101" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>The Eastern Company</t>
+          <t>Healthcare Realty Trust Incorporated</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>Cutlery, Handtools &amp; General Har</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>CDLX</t>
+          <t>MDLN</t>
         </is>
       </c>
       <c r="B102" s="17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C102" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D102" s="16" t="n">
-        <v>0.64</v>
+        <v>34.15</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>299.5495204</v>
+        <v>29437.82641572</v>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G102" s="10" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>Cardlytics, Inc.</t>
+          <t>Medline Inc.</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, D</t>
+          <t>Surgical &amp; Medical Instruments &amp;</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B103" s="17" t="n">
@@ -80677,10 +80703,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="16" t="n">
-        <v>5.88</v>
+        <v>30.66</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>1663.10279586</v>
+        <v>1530.00103608</v>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
@@ -80688,42 +80714,42 @@
         </is>
       </c>
       <c r="G103" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>Stagwell Inc.</t>
+          <t>Concentrix Corporation</t>
         </is>
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>Services-Advertising Agencies</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>ACRV</t>
+          <t>EML</t>
         </is>
       </c>
       <c r="B104" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="C104" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" s="16" t="n">
-        <v>1.7</v>
+        <v>21.37</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>67.19871453</v>
+        <v>142.81204352</v>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
@@ -80731,29 +80757,29 @@
         </is>
       </c>
       <c r="G104" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H104" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>Acrivon Therapeutics, Inc.</t>
+          <t>The Eastern Company</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>Pharmaceutical Preparations</t>
+          <t>Cutlery, Handtools &amp; General Har</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>CDLX</t>
         </is>
       </c>
       <c r="B105" s="17" t="n">
@@ -80763,40 +80789,40 @@
         <v>1</v>
       </c>
       <c r="D105" s="16" t="n">
-        <v>14.53</v>
+        <v>0.64</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>9269.53511472</v>
+        <v>299.5495204</v>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G105" s="10" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H105" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>Core Scientific, Inc.</t>
+          <t>Cardlytics, Inc.</t>
         </is>
       </c>
       <c r="K105" s="12" t="inlineStr">
         <is>
-          <t>Finance Services</t>
+          <t>Services-Computer Programming, D</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="B106" s="17" t="n">
@@ -80806,40 +80832,40 @@
         <v>1</v>
       </c>
       <c r="D106" s="16" t="n">
-        <v>4.14</v>
+        <v>5.88</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>253.54585542</v>
+        <v>1663.10279586</v>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G106" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H106" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>Fossil Group, Inc.</t>
+          <t>Stagwell Inc.</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>Watches, Clocks, Clockwork Opera</t>
+          <t>Services-Advertising Agencies</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>KNSL</t>
+          <t>ACRV</t>
         </is>
       </c>
       <c r="B107" s="17" t="n">
@@ -80849,40 +80875,40 @@
         <v>1</v>
       </c>
       <c r="D107" s="16" t="n">
-        <v>304</v>
+        <v>1.7</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>7122.95164815</v>
+        <v>67.19871453</v>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G107" s="10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H107" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="10" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>Kinsale Capital Group, Inc.</t>
+          <t>Acrivon Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
-          <t>Fire, Marine &amp; Casualty Insuranc</t>
+          <t>Pharmaceutical Preparations</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="B108" s="17" t="n">
@@ -80892,33 +80918,205 @@
         <v>1</v>
       </c>
       <c r="D108" s="16" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>9269.53511472</v>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc.</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>Finance Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>FOSL</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>253.54585542</v>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>Fossil Group, Inc.</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr">
+        <is>
+          <t>Watches, Clocks, Clockwork Opera</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>KNSL</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C110" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="16" t="n">
+        <v>304</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>7122.95164815</v>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>Kinsale Capital Group, Inc.</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr">
+        <is>
+          <t>Fire, Marine &amp; Casualty Insuranc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="16" t="n">
         <v>13.38</v>
       </c>
-      <c r="E108" s="11" t="n">
+      <c r="E111" s="11" t="n">
         <v>5421.86655696</v>
       </c>
-      <c r="F108" s="12" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="G108" s="10" t="n">
+      <c r="G111" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="H108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="12" t="inlineStr">
+      <c r="H111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
         <is>
           <t>Lyft, Inc.</t>
         </is>
       </c>
-      <c r="K108" s="12" t="inlineStr">
+      <c r="K111" s="12" t="inlineStr">
         <is>
           <t>Services-Business Services, NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>MOH</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C112" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>125.16</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>10178.777</v>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>Molina Healthcare, Inc.</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr">
+        <is>
+          <t>Hospital &amp; Medical Service Plans</t>
         </is>
       </c>
     </row>
